--- a/test-laporan.xlsx
+++ b/test-laporan.xlsx
@@ -427,7 +427,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Waktu Unduh: Minggu, 18 Oktober 2026 pukul 16.37.54 WIB · Total Data: 2 Baris</v>
+        <v>Waktu Unduh: Minggu, 18 Oktober 2026 pukul 16.47.05 WIB · Total Data: 2 Baris</v>
       </c>
     </row>
     <row r="7">

--- a/test-laporan.xlsx
+++ b/test-laporan.xlsx
@@ -427,7 +427,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Waktu Unduh: Minggu, 18 Oktober 2026 pukul 16.47.05 WIB · Total Data: 2 Baris</v>
+        <v>Waktu Unduh: Minggu, 18 Oktober 2026 pukul 16.55.03 WIB · Total Data: 2 Baris</v>
       </c>
     </row>
     <row r="7">

--- a/test-laporan.xlsx
+++ b/test-laporan.xlsx
@@ -427,7 +427,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Waktu Unduh: Minggu, 18 Oktober 2026 pukul 16.55.03 WIB · Total Data: 2 Baris</v>
+        <v>Waktu Unduh: Minggu, 18 Oktober 2026 pukul 17.18.02 WIB · Total Data: 2 Baris</v>
       </c>
     </row>
     <row r="7">

--- a/test-laporan.xlsx
+++ b/test-laporan.xlsx
@@ -427,7 +427,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Waktu Unduh: Minggu, 18 Oktober 2026 pukul 17.18.02 WIB · Total Data: 2 Baris</v>
+        <v>Waktu Unduh: Minggu, 18 Oktober 2026 pukul 17.34.44 WIB · Total Data: 2 Baris</v>
       </c>
     </row>
     <row r="7">

--- a/test-laporan.xlsx
+++ b/test-laporan.xlsx
@@ -427,7 +427,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Waktu Unduh: Minggu, 18 Oktober 2026 pukul 17.34.44 WIB · Total Data: 2 Baris</v>
+        <v>Waktu Unduh: Minggu, 18 Oktober 2026 pukul 17.44.00 WIB · Total Data: 2 Baris</v>
       </c>
     </row>
     <row r="7">

--- a/test-laporan.xlsx
+++ b/test-laporan.xlsx
@@ -427,7 +427,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Waktu Unduh: Minggu, 18 Oktober 2026 pukul 17.44.00 WIB · Total Data: 2 Baris</v>
+        <v>Waktu Unduh: Minggu, 18 Oktober 2026 pukul 17.53.00 WIB · Total Data: 2 Baris</v>
       </c>
     </row>
     <row r="7">
